--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Petugas_KELUARGA KHUSUS.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Petugas_KELUARGA KHUSUS.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,187 +429,187 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama Petugas</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email Petugas</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jabatan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Persentase Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Petugas_KELUARGA KHUSUS.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_Petugas_KELUARGA KHUSUS.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,187 +417,187 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama Petugas</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email Petugas</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Jabatan</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Hasil Pendataan PPL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>PENDATAAN K1 - Jumlah Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Persentase Bangunan Keluarga Khusus Didata</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -723,19 +711,19 @@
         <v>447</v>
       </c>
       <c r="AG2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -846,7 +834,7 @@
         <v>342</v>
       </c>
       <c r="AG3" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -858,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4">
@@ -969,7 +957,7 @@
         <v>249</v>
       </c>
       <c r="AG4" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -978,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5">
@@ -1092,7 +1080,7 @@
         <v>233</v>
       </c>
       <c r="AG5" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1104,7 +1092,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -1215,19 +1203,19 @@
         <v>395</v>
       </c>
       <c r="AG6" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
@@ -1338,19 +1326,19 @@
         <v>285</v>
       </c>
       <c r="AG7" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AH7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8">
@@ -1461,19 +1449,19 @@
         <v>389</v>
       </c>
       <c r="AG8" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
@@ -1584,19 +1572,19 @@
         <v>278</v>
       </c>
       <c r="AG9" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1707,19 +1695,19 @@
         <v>271</v>
       </c>
       <c r="AG10" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -1830,19 +1818,19 @@
         <v>386</v>
       </c>
       <c r="AG11" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12">
@@ -1953,19 +1941,19 @@
         <v>493</v>
       </c>
       <c r="AG12" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="13">
@@ -2076,19 +2064,19 @@
         <v>347</v>
       </c>
       <c r="AG13" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14">
@@ -2199,19 +2187,19 @@
         <v>308</v>
       </c>
       <c r="AG14" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AH14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15">
@@ -2322,19 +2310,19 @@
         <v>382</v>
       </c>
       <c r="AG15" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16">
@@ -2376,7 +2364,7 @@
         <v>71</v>
       </c>
       <c r="J16" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -2397,22 +2385,22 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="T16" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="U16" t="n">
         <v>71</v>
       </c>
       <c r="V16" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="W16" t="n">
         <v>2</v>
@@ -2433,31 +2421,31 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AF16" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AG16" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AH16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17">
@@ -2568,19 +2556,19 @@
         <v>377</v>
       </c>
       <c r="AG17" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18">
@@ -2691,19 +2679,19 @@
         <v>318</v>
       </c>
       <c r="AG18" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19">
@@ -2814,19 +2802,19 @@
         <v>307</v>
       </c>
       <c r="AG19" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20">
@@ -2937,19 +2925,19 @@
         <v>253</v>
       </c>
       <c r="AG20" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK20" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
@@ -2988,19 +2976,19 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="J21" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -3012,31 +3000,31 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="T21" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="U21" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="V21" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="W21" t="n">
         <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="Y21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3048,31 +3036,31 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AF21" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AG21" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AI21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22">
@@ -3183,19 +3171,19 @@
         <v>423</v>
       </c>
       <c r="AG22" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23">
@@ -3306,19 +3294,19 @@
         <v>282</v>
       </c>
       <c r="AG23" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
@@ -3429,25 +3417,25 @@
         <v>368</v>
       </c>
       <c r="AG24" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3480,19 +3468,19 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="K25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3504,31 +3492,31 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="T25" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="U25" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="W25" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -3540,31 +3528,31 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AG25" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -3675,19 +3663,19 @@
         <v>387</v>
       </c>
       <c r="AG26" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27">
@@ -3798,10 +3786,10 @@
         <v>375</v>
       </c>
       <c r="AG27" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AH27" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3810,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="28">
@@ -3921,19 +3909,19 @@
         <v>343</v>
       </c>
       <c r="AG28" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="29">
@@ -4044,19 +4032,19 @@
         <v>380</v>
       </c>
       <c r="AG29" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
@@ -4167,19 +4155,19 @@
         <v>201</v>
       </c>
       <c r="AG30" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
@@ -4290,19 +4278,19 @@
         <v>281</v>
       </c>
       <c r="AG31" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32">
@@ -4413,19 +4401,19 @@
         <v>282</v>
       </c>
       <c r="AG32" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AH32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI32" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33">
@@ -4536,19 +4524,19 @@
         <v>450</v>
       </c>
       <c r="AG33" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AH33" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AI33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34">
@@ -4659,19 +4647,19 @@
         <v>243</v>
       </c>
       <c r="AG34" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35">
@@ -4782,19 +4770,19 @@
         <v>477</v>
       </c>
       <c r="AG35" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="36">
@@ -4905,19 +4893,19 @@
         <v>518</v>
       </c>
       <c r="AG36" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="37">
@@ -4943,7 +4931,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -5028,19 +5016,19 @@
         <v>365</v>
       </c>
       <c r="AG37" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AI37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38">
@@ -5066,7 +5054,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -5151,19 +5139,19 @@
         <v>313</v>
       </c>
       <c r="AG38" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI38" t="n">
         <v>4</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
@@ -5274,19 +5262,19 @@
         <v>399</v>
       </c>
       <c r="AG39" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40">
@@ -5397,19 +5385,19 @@
         <v>350</v>
       </c>
       <c r="AG40" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41">
@@ -5520,19 +5508,19 @@
         <v>387</v>
       </c>
       <c r="AG41" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AI41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42">
@@ -5643,7 +5631,7 @@
         <v>388</v>
       </c>
       <c r="AG42" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -5652,10 +5640,10 @@
         <v>13</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43">
@@ -5766,7 +5754,7 @@
         <v>381</v>
       </c>
       <c r="AG43" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -5775,21 +5763,21 @@
         <v>9</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK43" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5799,12 +5787,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -5817,102 +5805,102 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="J44" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="T44" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="U44" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="V44" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="W44" t="n">
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE44" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AF44" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK44" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5922,12 +5910,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5940,19 +5928,19 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="J45" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5964,31 +5952,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="R45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="T45" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="U45" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="V45" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="Y45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6000,42 +5988,42 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AD45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AF45" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AG45" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AH45" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AI45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6045,12 +6033,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -6063,102 +6051,102 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="J46" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L46" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="T46" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="U46" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="V46" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="X46" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AF46" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AG46" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AH46" t="n">
         <v>1</v>
       </c>
       <c r="AI46" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6168,12 +6156,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -6186,55 +6174,55 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J47" t="n">
-        <v>218</v>
+        <v>334</v>
       </c>
       <c r="K47" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>25</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>485</v>
+      </c>
+      <c r="T47" t="n">
+        <v>364</v>
+      </c>
+      <c r="U47" t="n">
+        <v>121</v>
+      </c>
+      <c r="V47" t="n">
+        <v>334</v>
+      </c>
+      <c r="W47" t="n">
         <v>4</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>42</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>428</v>
-      </c>
-      <c r="T47" t="n">
-        <v>299</v>
-      </c>
-      <c r="U47" t="n">
-        <v>128</v>
-      </c>
-      <c r="V47" t="n">
-        <v>218</v>
-      </c>
-      <c r="W47" t="n">
-        <v>35</v>
-      </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -6246,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE47" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AF47" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -6267,21 +6255,21 @@
         <v>4</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6291,12 +6279,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -6309,102 +6297,102 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="J48" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="T48" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="U48" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="V48" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="W48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z48" t="n">
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AD48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE48" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AF48" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AG48" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6414,12 +6402,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -6432,102 +6420,102 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="J49" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="T49" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="U49" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="V49" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="W49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AD49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AF49" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AG49" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6537,12 +6525,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -6555,102 +6543,102 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="J50" t="n">
-        <v>398</v>
+        <v>331</v>
       </c>
       <c r="K50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L50" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>50</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>482</v>
+      </c>
+      <c r="T50" t="n">
+        <v>390</v>
+      </c>
+      <c r="U50" t="n">
+        <v>89</v>
+      </c>
+      <c r="V50" t="n">
+        <v>331</v>
+      </c>
+      <c r="W50" t="n">
+        <v>8</v>
+      </c>
+      <c r="X50" t="n">
         <v>3</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>52</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>539</v>
-      </c>
-      <c r="T50" t="n">
-        <v>460</v>
-      </c>
-      <c r="U50" t="n">
-        <v>61</v>
-      </c>
-      <c r="V50" t="n">
-        <v>398</v>
-      </c>
-      <c r="W50" t="n">
-        <v>7</v>
-      </c>
-      <c r="X50" t="n">
-        <v>18</v>
-      </c>
       <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>482</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>390</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>89</v>
+      </c>
+      <c r="AH50" t="n">
         <v>3</v>
       </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>52</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>539</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>460</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>395</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
       <c r="AI50" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AJ50" t="n">
         <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6660,12 +6648,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -6678,16 +6666,16 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="J51" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="K51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6696,34 +6684,34 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="T51" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="U51" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="V51" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="W51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -6732,28 +6720,28 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AD51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AF51" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AG51" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -6762,18 +6750,18 @@
         <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6801,102 +6789,102 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="J52" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="T52" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="U52" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="V52" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X52" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE52" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AF52" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AG52" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AH52" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AI52" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AJ52" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AK52" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6906,12 +6894,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -6924,22 +6912,22 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="J53" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6948,34 +6936,34 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="T53" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="U53" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="V53" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="W53" t="n">
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -6984,42 +6972,42 @@
         <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE53" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AF53" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AG53" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AH53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AI53" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -7029,12 +7017,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -7047,22 +7035,22 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="J54" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7071,34 +7059,34 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="R54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="T54" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="U54" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="V54" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Y54" t="n">
         <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7107,42 +7095,42 @@
         <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AD54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE54" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AF54" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AI54" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AJ54" t="n">
         <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -7152,12 +7140,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -7170,19 +7158,19 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="J55" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="L55" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -7194,31 +7182,31 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="T55" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="U55" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="V55" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="W55" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="X55" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="n">
         <v>0</v>
@@ -7230,42 +7218,42 @@
         <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AD55" t="n">
         <v>1</v>
       </c>
       <c r="AE55" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AF55" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AG55" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -7275,12 +7263,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -7293,19 +7281,19 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="J56" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="K56" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -7317,31 +7305,31 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="T56" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="U56" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="V56" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="W56" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="Y56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
         <v>0</v>
@@ -7353,31 +7341,31 @@
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AD56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AF56" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AG56" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AH56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI56" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ56" t="n">
         <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57">
@@ -7488,19 +7476,19 @@
         <v>267</v>
       </c>
       <c r="AG57" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AH57" t="n">
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58">
@@ -7611,19 +7599,19 @@
         <v>364</v>
       </c>
       <c r="AG58" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AH58" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AI58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ58" t="n">
         <v>0</v>
       </c>
       <c r="AK58" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59">
@@ -7734,19 +7722,19 @@
         <v>289</v>
       </c>
       <c r="AG59" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI59" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60">
@@ -7857,19 +7845,19 @@
         <v>238</v>
       </c>
       <c r="AG60" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AH60" t="n">
         <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61">
@@ -7980,19 +7968,19 @@
         <v>440</v>
       </c>
       <c r="AG61" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI61" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AJ61" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AK61" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="62">
@@ -8103,19 +8091,19 @@
         <v>373</v>
       </c>
       <c r="AG62" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63">
@@ -8226,19 +8214,19 @@
         <v>394</v>
       </c>
       <c r="AG63" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AH63" t="n">
         <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64">
@@ -8349,19 +8337,19 @@
         <v>357</v>
       </c>
       <c r="AG64" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AH64" t="n">
         <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65">
@@ -8472,19 +8460,19 @@
         <v>397</v>
       </c>
       <c r="AG65" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AH65" t="n">
         <v>0</v>
       </c>
       <c r="AI65" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK65" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66">
@@ -8595,19 +8583,19 @@
         <v>255</v>
       </c>
       <c r="AG66" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AH66" t="n">
         <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AK66" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="67">
@@ -8718,19 +8706,19 @@
         <v>504</v>
       </c>
       <c r="AG67" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI67" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AJ67" t="n">
         <v>1</v>
       </c>
       <c r="AK67" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="68">
@@ -8841,19 +8829,19 @@
         <v>300</v>
       </c>
       <c r="AG68" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AH68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI68" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AJ68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69">
@@ -8964,19 +8952,19 @@
         <v>224</v>
       </c>
       <c r="AG69" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AH69" t="n">
         <v>0</v>
       </c>
       <c r="AI69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ69" t="n">
         <v>0</v>
       </c>
       <c r="AK69" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70">
@@ -9087,19 +9075,19 @@
         <v>441</v>
       </c>
       <c r="AG70" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AH70" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ70" t="n">
         <v>0</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71">
@@ -9210,19 +9198,19 @@
         <v>578</v>
       </c>
       <c r="AG71" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AH71" t="n">
         <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="72">
@@ -9333,19 +9321,19 @@
         <v>331</v>
       </c>
       <c r="AG72" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI72" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AJ72" t="n">
         <v>0</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73">
@@ -9456,10 +9444,10 @@
         <v>472</v>
       </c>
       <c r="AG73" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AH73" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9468,7 +9456,7 @@
         <v>0</v>
       </c>
       <c r="AK73" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="74">
@@ -9579,19 +9567,19 @@
         <v>283</v>
       </c>
       <c r="AG74" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AH74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI74" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="75">
@@ -9702,19 +9690,19 @@
         <v>251</v>
       </c>
       <c r="AG75" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AH75" t="n">
         <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76">
@@ -9825,19 +9813,19 @@
         <v>430</v>
       </c>
       <c r="AG76" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AH76" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AI76" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77">
@@ -9948,19 +9936,19 @@
         <v>306</v>
       </c>
       <c r="AG77" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AH77" t="n">
         <v>0</v>
       </c>
       <c r="AI77" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78">
@@ -10071,7 +10059,7 @@
         <v>394</v>
       </c>
       <c r="AG78" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AH78" t="n">
         <v>0</v>
@@ -10080,21 +10068,21 @@
         <v>6</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK78" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -10104,16 +10092,16 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -10122,91 +10110,91 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="J79" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N79" t="n">
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="T79" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="U79" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="V79" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y79" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Z79" t="n">
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
         <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AD79" t="n">
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AF79" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AG79" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AH79" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AI79" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK79" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80">
@@ -10317,19 +10305,19 @@
         <v>292</v>
       </c>
       <c r="AG80" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AH80" t="n">
         <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
         <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81">
@@ -10440,19 +10428,19 @@
         <v>330</v>
       </c>
       <c r="AG81" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AH81" t="n">
         <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="82">
@@ -10563,19 +10551,19 @@
         <v>299</v>
       </c>
       <c r="AG82" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AH82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83">
@@ -10686,19 +10674,19 @@
         <v>316</v>
       </c>
       <c r="AG83" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AH83" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84">
@@ -10809,19 +10797,19 @@
         <v>299</v>
       </c>
       <c r="AG84" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AH84" t="n">
         <v>0</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AK84" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85">
@@ -10932,19 +10920,19 @@
         <v>327</v>
       </c>
       <c r="AG85" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AH85" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AI85" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK85" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86">
@@ -11055,19 +11043,19 @@
         <v>278</v>
       </c>
       <c r="AG86" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AH86" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AI86" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AK86" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="87">
@@ -11178,19 +11166,19 @@
         <v>362</v>
       </c>
       <c r="AG87" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AH87" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AI87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK87" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="88">
@@ -11301,19 +11289,19 @@
         <v>333</v>
       </c>
       <c r="AG88" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AH88" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="n">
         <v>2</v>
       </c>
-      <c r="AJ88" t="n">
-        <v>0</v>
-      </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89">
@@ -11424,19 +11412,19 @@
         <v>239</v>
       </c>
       <c r="AG89" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI89" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AJ89" t="n">
         <v>0</v>
       </c>
       <c r="AK89" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90">
@@ -11547,19 +11535,19 @@
         <v>316</v>
       </c>
       <c r="AG90" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AH90" t="n">
         <v>0</v>
       </c>
       <c r="AI90" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AJ90" t="n">
         <v>0</v>
       </c>
       <c r="AK90" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="91">
@@ -11670,19 +11658,19 @@
         <v>360</v>
       </c>
       <c r="AG91" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI91" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AJ91" t="n">
         <v>0</v>
       </c>
       <c r="AK91" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92">
@@ -11793,19 +11781,19 @@
         <v>381</v>
       </c>
       <c r="AG92" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AH92" t="n">
         <v>0</v>
       </c>
       <c r="AI92" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AJ92" t="n">
         <v>0</v>
       </c>
       <c r="AK92" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="93">
@@ -11916,10 +11904,10 @@
         <v>278</v>
       </c>
       <c r="AG93" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AH93" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AI93" t="n">
         <v>4</v>
@@ -11928,7 +11916,7 @@
         <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="94">
@@ -12039,19 +12027,19 @@
         <v>382</v>
       </c>
       <c r="AG94" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AH94" t="n">
         <v>0</v>
       </c>
       <c r="AI94" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK94" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="95">
@@ -12162,19 +12150,19 @@
         <v>366</v>
       </c>
       <c r="AG95" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AH95" t="n">
         <v>0</v>
       </c>
       <c r="AI95" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK95" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96">
@@ -12285,19 +12273,19 @@
         <v>360</v>
       </c>
       <c r="AG96" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AH96" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AI96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK96" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="97">
@@ -12408,19 +12396,19 @@
         <v>248</v>
       </c>
       <c r="AG97" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI97" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AJ97" t="n">
         <v>0</v>
       </c>
       <c r="AK97" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="98">
@@ -12531,19 +12519,19 @@
         <v>347</v>
       </c>
       <c r="AG98" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AH98" t="n">
         <v>0</v>
       </c>
       <c r="AI98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="99">
@@ -12654,19 +12642,19 @@
         <v>277</v>
       </c>
       <c r="AG99" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AH99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK99" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="100">
@@ -12777,19 +12765,19 @@
         <v>399</v>
       </c>
       <c r="AG100" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AH100" t="n">
         <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ100" t="n">
         <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="101">
@@ -12815,7 +12803,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -12900,19 +12888,19 @@
         <v>318</v>
       </c>
       <c r="AG101" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AI101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK101" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102">
@@ -13023,19 +13011,19 @@
         <v>427</v>
       </c>
       <c r="AG102" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AJ102" t="n">
         <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103">
@@ -13061,7 +13049,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -13146,19 +13134,19 @@
         <v>296</v>
       </c>
       <c r="AG103" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AH103" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AI103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK103" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104">
@@ -13200,7 +13188,7 @@
         <v>87</v>
       </c>
       <c r="J104" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="K104" t="n">
         <v>16</v>
@@ -13221,22 +13209,22 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="T104" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="U104" t="n">
         <v>87</v>
       </c>
       <c r="V104" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="W104" t="n">
         <v>16</v>
@@ -13257,31 +13245,31 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AD104" t="n">
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AF104" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AG104" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI104" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AJ104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK104" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="105">
@@ -13392,19 +13380,19 @@
         <v>395</v>
       </c>
       <c r="AG105" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AH105" t="n">
         <v>1</v>
       </c>
       <c r="AI105" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AJ105" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AK105" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="106">
@@ -13515,19 +13503,19 @@
         <v>307</v>
       </c>
       <c r="AG106" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AH106" t="n">
         <v>0</v>
       </c>
       <c r="AI106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AJ106" t="n">
         <v>0</v>
       </c>
       <c r="AK106" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="107">
@@ -13638,19 +13626,19 @@
         <v>368</v>
       </c>
       <c r="AG107" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AH107" t="n">
         <v>0</v>
       </c>
       <c r="AI107" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AJ107" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK107" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108">
@@ -13761,10 +13749,10 @@
         <v>313</v>
       </c>
       <c r="AG108" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AH108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>2</v>
@@ -13773,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="AK108" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="109">
@@ -13884,10 +13872,10 @@
         <v>404</v>
       </c>
       <c r="AG109" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -13896,7 +13884,7 @@
         <v>3</v>
       </c>
       <c r="AK109" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110">
@@ -14007,19 +13995,19 @@
         <v>307</v>
       </c>
       <c r="AG110" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AH110" t="n">
         <v>0</v>
       </c>
       <c r="AI110" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ110" t="n">
         <v>0</v>
       </c>
       <c r="AK110" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="111">
@@ -14130,19 +14118,19 @@
         <v>262</v>
       </c>
       <c r="AG111" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK111" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112">
@@ -14253,19 +14241,19 @@
         <v>442</v>
       </c>
       <c r="AG112" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AH112" t="n">
         <v>0</v>
       </c>
       <c r="AI112" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AK112" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="113">
@@ -14376,19 +14364,19 @@
         <v>561</v>
       </c>
       <c r="AG113" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
         <v>0</v>
       </c>
       <c r="AI113" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ113" t="n">
         <v>0</v>
       </c>
       <c r="AK113" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="114">
@@ -14499,19 +14487,19 @@
         <v>271</v>
       </c>
       <c r="AG114" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ114" t="n">
         <v>0</v>
       </c>
       <c r="AK114" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115">
@@ -14622,30 +14610,30 @@
         <v>292</v>
       </c>
       <c r="AG115" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AH115" t="n">
         <v>0</v>
       </c>
       <c r="AI115" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AJ115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK115" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -14655,16 +14643,16 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -14673,25 +14661,25 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="J116" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="K116" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N116" t="n">
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P116" t="n">
         <v>0</v>
@@ -14703,31 +14691,31 @@
         <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="T116" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="U116" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="V116" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="W116" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z116" t="n">
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB116" t="n">
         <v>0</v>
@@ -14739,36 +14727,36 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AF116" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AG116" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AH116" t="n">
         <v>0</v>
       </c>
       <c r="AI116" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AJ116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK116" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14778,12 +14766,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -14796,13 +14784,13 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="J117" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -14823,22 +14811,22 @@
         <v>42</v>
       </c>
       <c r="R117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="T117" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="U117" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="V117" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -14859,39 +14847,39 @@
         <v>42</v>
       </c>
       <c r="AD117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AF117" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AG117" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AH117" t="n">
         <v>0</v>
       </c>
       <c r="AI117" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ117" t="n">
         <v>0</v>
       </c>
       <c r="AK117" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14901,12 +14889,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -14919,13 +14907,13 @@
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="J118" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="K118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -14937,31 +14925,31 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="R118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S118" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="T118" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="U118" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="V118" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="W118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
         <v>0</v>
@@ -14973,48 +14961,48 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
         <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AD118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE118" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AF118" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AG118" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AH118" t="n">
         <v>0</v>
       </c>
       <c r="AI118" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ118" t="n">
         <v>0</v>
       </c>
       <c r="AK118" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -15024,12 +15012,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -15042,13 +15030,13 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="J119" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="K119" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -15060,31 +15048,31 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>58</v>
+      </c>
+      <c r="R119" t="n">
         <v>3</v>
       </c>
-      <c r="P119" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>96</v>
-      </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="T119" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="U119" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="V119" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="W119" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -15096,48 +15084,48 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD119" t="n">
         <v>3</v>
       </c>
-      <c r="AB119" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC119" t="n">
-        <v>96</v>
-      </c>
-      <c r="AD119" t="n">
-        <v>0</v>
-      </c>
       <c r="AE119" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AF119" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AG119" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AH119" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AI119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ119" t="n">
         <v>0</v>
       </c>
       <c r="AK119" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15147,12 +15135,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -15165,16 +15153,16 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="J120" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="K120" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -15183,34 +15171,34 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P120" t="n">
         <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="R120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="T120" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="U120" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="V120" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="W120" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="X120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y120" t="n">
         <v>0</v>
@@ -15219,48 +15207,48 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB120" t="n">
         <v>0</v>
       </c>
       <c r="AC120" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AD120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AF120" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AG120" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AH120" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI120" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ120" t="n">
         <v>0</v>
       </c>
       <c r="AK120" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -15270,16 +15258,16 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -15288,16 +15276,16 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="J121" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="K121" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -15306,34 +15294,34 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P121" t="n">
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="T121" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="U121" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="V121" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="W121" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y121" t="n">
         <v>0</v>
@@ -15342,48 +15330,48 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE121" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AF121" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AG121" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AH121" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ121" t="n">
         <v>0</v>
       </c>
       <c r="AK121" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -15393,16 +15381,16 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -15411,102 +15399,102 @@
         <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="J122" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
         <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P122" t="n">
         <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="R122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="T122" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="U122" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="V122" t="n">
-        <v>338</v>
+        <v>256</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB122" t="n">
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AD122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AF122" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AG122" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AH122" t="n">
         <v>0</v>
       </c>
       <c r="AI122" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AJ122" t="n">
         <v>0</v>
       </c>
       <c r="AK122" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -15534,19 +15522,19 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="J123" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
       </c>
       <c r="L123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
@@ -15558,31 +15546,31 @@
         <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="R123" t="n">
         <v>1</v>
       </c>
       <c r="S123" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="T123" t="n">
         <v>371</v>
       </c>
       <c r="U123" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="V123" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="W123" t="n">
         <v>0</v>
       </c>
       <c r="X123" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z123" t="n">
         <v>0</v>
@@ -15594,42 +15582,42 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AD123" t="n">
         <v>1</v>
       </c>
       <c r="AE123" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AF123" t="n">
         <v>371</v>
       </c>
       <c r="AG123" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AH123" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AI123" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK123" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -15639,12 +15627,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -15657,16 +15645,16 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="J124" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -15675,84 +15663,84 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>44</v>
+      </c>
+      <c r="R124" t="n">
+        <v>1</v>
+      </c>
+      <c r="S124" t="n">
+        <v>514</v>
+      </c>
+      <c r="T124" t="n">
+        <v>371</v>
+      </c>
+      <c r="U124" t="n">
+        <v>141</v>
+      </c>
+      <c r="V124" t="n">
+        <v>326</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
         <v>2</v>
       </c>
-      <c r="P124" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>79</v>
-      </c>
-      <c r="R124" t="n">
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>514</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>371</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>141</v>
+      </c>
+      <c r="AH124" t="n">
         <v>2</v>
       </c>
-      <c r="S124" t="n">
-        <v>372</v>
-      </c>
-      <c r="T124" t="n">
-        <v>372</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>288</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>79</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE124" t="n">
-        <v>372</v>
-      </c>
-      <c r="AF124" t="n">
-        <v>372</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>303</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
       <c r="AI124" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ124" t="n">
         <v>0</v>
       </c>
       <c r="AK124" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -15762,12 +15750,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -15780,102 +15768,102 @@
         <v>0</v>
       </c>
       <c r="I125" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
         <v>2</v>
       </c>
-      <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" t="n">
-        <v>1</v>
-      </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="R125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S125" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="T125" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="U125" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
         <v>2</v>
       </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>1</v>
-      </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC125" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AD125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE125" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AF125" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AG125" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AH125" t="n">
         <v>0</v>
       </c>
       <c r="AI125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ125" t="n">
         <v>0</v>
       </c>
       <c r="AK125" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -15885,12 +15873,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -15903,102 +15891,102 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="J126" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S126" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="T126" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="U126" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="V126" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="W126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X126" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB126" t="n">
         <v>0</v>
       </c>
       <c r="AC126" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE126" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AF126" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AG126" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AH126" t="n">
         <v>0</v>
       </c>
       <c r="AI126" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AJ126" t="n">
         <v>0</v>
       </c>
       <c r="AK126" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -16008,12 +15996,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -16026,19 +16014,19 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="J127" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="K127" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N127" t="n">
         <v>0</v>
@@ -16050,31 +16038,31 @@
         <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
       <c r="S127" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="T127" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="U127" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="V127" t="n">
-        <v>317</v>
+        <v>268</v>
       </c>
       <c r="W127" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X127" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Y127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
@@ -16086,42 +16074,42 @@
         <v>0</v>
       </c>
       <c r="AC127" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AD127" t="n">
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AF127" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG127" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AH127" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK127" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -16131,12 +16119,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -16149,19 +16137,19 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="J128" t="n">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="K128" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -16173,78 +16161,78 @@
         <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="R128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="T128" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="U128" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="V128" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="W128" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X128" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z128" t="n">
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
         <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AD128" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AF128" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AG128" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AH128" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ128" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK128" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -16272,19 +16260,19 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J129" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L129" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N129" t="n">
         <v>0</v>
@@ -16296,28 +16284,28 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="R129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S129" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="T129" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="U129" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="V129" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="W129" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X129" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="Y129" t="n">
         <v>0</v>
@@ -16326,48 +16314,48 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB129" t="n">
         <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AD129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE129" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AF129" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AG129" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AH129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI129" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AJ129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK129" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -16377,12 +16365,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -16395,16 +16383,16 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="J130" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="K130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M130" t="n">
         <v>0</v>
@@ -16419,28 +16407,28 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S130" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="T130" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="U130" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="V130" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="W130" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="X130" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Y130" t="n">
         <v>0</v>
@@ -16455,42 +16443,42 @@
         <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE130" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AF130" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AG130" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AH130" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AI130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ130" t="n">
         <v>0</v>
       </c>
       <c r="AK130" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yustindurian@gmail.com</t>
+          <t>yudhistiratangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -16500,12 +16488,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -16518,13 +16506,13 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J131" t="n">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="K131" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -16536,31 +16524,31 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
         <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
-        <v>456</v>
+        <v>400</v>
       </c>
       <c r="T131" t="n">
-        <v>325</v>
+        <v>261</v>
       </c>
       <c r="U131" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="V131" t="n">
-        <v>278</v>
+        <v>209</v>
       </c>
       <c r="W131" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X131" t="n">
         <v>0</v>
@@ -16572,63 +16560,63 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
         <v>0</v>
       </c>
       <c r="AC131" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="AD131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>456</v>
+        <v>400</v>
       </c>
       <c r="AF131" t="n">
-        <v>325</v>
+        <v>261</v>
       </c>
       <c r="AG131" t="n">
-        <v>368</v>
+        <v>139</v>
       </c>
       <c r="AH131" t="n">
         <v>0</v>
       </c>
       <c r="AI131" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ131" t="n">
         <v>0</v>
       </c>
       <c r="AK131" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>UNASSIGNED</t>
+          <t>yustindurian@gmail.com</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PML</t>
+          <t>PCL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -16641,13 +16629,13 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -16659,31 +16647,31 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
         <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S132" t="n">
-        <v>1</v>
+        <v>456</v>
       </c>
       <c r="T132" t="n">
-        <v>1</v>
+        <v>325</v>
       </c>
       <c r="U132" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="V132" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="W132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X132" t="n">
         <v>0</v>
@@ -16695,37 +16683,37 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB132" t="n">
         <v>0</v>
       </c>
       <c r="AC132" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="AD132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE132" t="n">
-        <v>1</v>
+        <v>456</v>
       </c>
       <c r="AF132" t="n">
-        <v>1</v>
+        <v>325</v>
       </c>
       <c r="AG132" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="AH132" t="n">
         <v>0</v>
       </c>
       <c r="AI132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ132" t="n">
         <v>0</v>
       </c>
       <c r="AK132" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="133">
@@ -16751,7 +16739,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -16836,19 +16824,19 @@
         <v>1608</v>
       </c>
       <c r="AG133" t="n">
-        <v>2226</v>
+        <v>751</v>
       </c>
       <c r="AH133" t="n">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="AI133" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK133" t="n">
-        <v>0</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="134">
@@ -16959,19 +16947,19 @@
         <v>2319</v>
       </c>
       <c r="AG134" t="n">
-        <v>2391</v>
+        <v>605</v>
       </c>
       <c r="AH134" t="n">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="AI134" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ134" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AK134" t="n">
-        <v>8</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="135">
@@ -17082,19 +17070,19 @@
         <v>1979</v>
       </c>
       <c r="AG135" t="n">
-        <v>2273</v>
+        <v>758</v>
       </c>
       <c r="AH135" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI135" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AJ135" t="n">
         <v>0</v>
       </c>
       <c r="AK135" t="n">
-        <v>0</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="136">
@@ -17205,19 +17193,19 @@
         <v>1720</v>
       </c>
       <c r="AG136" t="n">
-        <v>2079</v>
+        <v>940</v>
       </c>
       <c r="AH136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI136" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="AJ136" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AK136" t="n">
-        <v>0</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="137">
@@ -17328,19 +17316,19 @@
         <v>2460</v>
       </c>
       <c r="AG137" t="n">
-        <v>2283</v>
+        <v>473</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI137" t="n">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="AJ137" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK137" t="n">
-        <v>21</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="138">
@@ -17451,19 +17439,19 @@
         <v>1806</v>
       </c>
       <c r="AG138" t="n">
-        <v>2303</v>
+        <v>1003</v>
       </c>
       <c r="AH138" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="AI138" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AK138" t="n">
-        <v>4</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="139">
@@ -17574,19 +17562,19 @@
         <v>2106</v>
       </c>
       <c r="AG139" t="n">
-        <v>2464</v>
+        <v>815</v>
       </c>
       <c r="AH139" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AI139" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK139" t="n">
-        <v>0</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="140">
@@ -17697,19 +17685,19 @@
         <v>1799</v>
       </c>
       <c r="AG140" t="n">
-        <v>2009</v>
+        <v>720</v>
       </c>
       <c r="AH140" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AI140" t="n">
-        <v>57</v>
+        <v>334</v>
       </c>
       <c r="AJ140" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="AK140" t="n">
-        <v>1</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="141">
@@ -17748,19 +17736,19 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>747</v>
+        <v>665</v>
       </c>
       <c r="J141" t="n">
-        <v>1374</v>
+        <v>1405</v>
       </c>
       <c r="K141" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L141" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="M141" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -17772,31 +17760,31 @@
         <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="R141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S141" t="n">
-        <v>2426</v>
+        <v>2402</v>
       </c>
       <c r="T141" t="n">
-        <v>1568</v>
+        <v>1638</v>
       </c>
       <c r="U141" t="n">
-        <v>747</v>
+        <v>665</v>
       </c>
       <c r="V141" t="n">
-        <v>1374</v>
+        <v>1405</v>
       </c>
       <c r="W141" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="X141" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Y141" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z141" t="n">
         <v>0</v>
@@ -17808,31 +17796,31 @@
         <v>0</v>
       </c>
       <c r="AC141" t="n">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="AD141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE141" t="n">
-        <v>2426</v>
+        <v>2402</v>
       </c>
       <c r="AF141" t="n">
-        <v>1568</v>
+        <v>1638</v>
       </c>
       <c r="AG141" t="n">
-        <v>2036</v>
+        <v>665</v>
       </c>
       <c r="AH141" t="n">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="AI141" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AJ141" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="AK141" t="n">
-        <v>25</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="142">
@@ -17943,19 +17931,19 @@
         <v>1107</v>
       </c>
       <c r="AG142" t="n">
-        <v>1288</v>
+        <v>184</v>
       </c>
       <c r="AH142" t="n">
-        <v>11</v>
+        <v>199</v>
       </c>
       <c r="AI142" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AK142" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
     </row>
     <row r="143">
@@ -18066,19 +18054,19 @@
         <v>1433</v>
       </c>
       <c r="AG143" t="n">
-        <v>1827</v>
+        <v>689</v>
       </c>
       <c r="AH143" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI143" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="AJ143" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="AK143" t="n">
-        <v>2</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="144">
@@ -18189,19 +18177,19 @@
         <v>1748</v>
       </c>
       <c r="AG144" t="n">
-        <v>1746</v>
+        <v>418</v>
       </c>
       <c r="AH144" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AI144" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="AJ144" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK144" t="n">
-        <v>11</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="145">
@@ -18264,16 +18252,16 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R145" t="n">
         <v>12</v>
       </c>
       <c r="S145" t="n">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="T145" t="n">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="U145" t="n">
         <v>590</v>
@@ -18300,31 +18288,31 @@
         <v>0</v>
       </c>
       <c r="AC145" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AD145" t="n">
         <v>12</v>
       </c>
       <c r="AE145" t="n">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="AF145" t="n">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="AG145" t="n">
-        <v>1801</v>
+        <v>590</v>
       </c>
       <c r="AH145" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AI145" t="n">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="AJ145" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AK145" t="n">
-        <v>1</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="146">
@@ -18435,19 +18423,19 @@
         <v>1931</v>
       </c>
       <c r="AG146" t="n">
-        <v>1816</v>
+        <v>588</v>
       </c>
       <c r="AH146" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI146" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="AJ146" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AK146" t="n">
-        <v>0</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="147">
@@ -18558,19 +18546,19 @@
         <v>2258</v>
       </c>
       <c r="AG147" t="n">
-        <v>2199</v>
+        <v>598</v>
       </c>
       <c r="AH147" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="AI147" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="AJ147" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK147" t="n">
-        <v>0</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="148">
@@ -18681,19 +18669,19 @@
         <v>1426</v>
       </c>
       <c r="AG148" t="n">
-        <v>1779</v>
+        <v>764</v>
       </c>
       <c r="AH148" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI148" t="n">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK148" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
     </row>
     <row r="149">
@@ -18804,19 +18792,19 @@
         <v>2864</v>
       </c>
       <c r="AG149" t="n">
-        <v>2136</v>
+        <v>131</v>
       </c>
       <c r="AH149" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AI149" t="n">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK149" t="n">
-        <v>0</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="150">
@@ -18927,19 +18915,19 @@
         <v>2557</v>
       </c>
       <c r="AG150" t="n">
-        <v>2255</v>
+        <v>353</v>
       </c>
       <c r="AH150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="AJ150" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AK150" t="n">
-        <v>25</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="151">
@@ -19050,19 +19038,19 @@
         <v>1812</v>
       </c>
       <c r="AG151" t="n">
-        <v>1810</v>
+        <v>225</v>
       </c>
       <c r="AH151" t="n">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="AI151" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK151" t="n">
-        <v>1</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="152">
@@ -19173,19 +19161,19 @@
         <v>2249</v>
       </c>
       <c r="AG152" t="n">
-        <v>1936</v>
+        <v>372</v>
       </c>
       <c r="AH152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI152" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AJ152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AK152" t="n">
-        <v>0</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="153">
@@ -19296,19 +19284,19 @@
         <v>2510</v>
       </c>
       <c r="AG153" t="n">
-        <v>2231</v>
+        <v>425</v>
       </c>
       <c r="AH153" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="AI153" t="n">
+        <v>187</v>
+      </c>
+      <c r="AJ153" t="n">
         <v>54</v>
       </c>
-      <c r="AJ153" t="n">
-        <v>4</v>
-      </c>
       <c r="AK153" t="n">
-        <v>31</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="154">
@@ -19347,19 +19335,19 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>669</v>
+        <v>751</v>
       </c>
       <c r="J154" t="n">
-        <v>1867</v>
+        <v>1836</v>
       </c>
       <c r="K154" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L154" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="M154" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N154" t="n">
         <v>0</v>
@@ -19371,31 +19359,31 @@
         <v>0</v>
       </c>
       <c r="Q154" t="n">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="R154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S154" t="n">
-        <v>2935</v>
+        <v>2959</v>
       </c>
       <c r="T154" t="n">
-        <v>2229</v>
+        <v>2159</v>
       </c>
       <c r="U154" t="n">
-        <v>671</v>
+        <v>753</v>
       </c>
       <c r="V154" t="n">
-        <v>1867</v>
+        <v>1836</v>
       </c>
       <c r="W154" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="X154" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="Y154" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Z154" t="n">
         <v>0</v>
@@ -19407,31 +19395,31 @@
         <v>0</v>
       </c>
       <c r="AC154" t="n">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="AD154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE154" t="n">
-        <v>2935</v>
+        <v>2959</v>
       </c>
       <c r="AF154" t="n">
-        <v>2227</v>
+        <v>2157</v>
       </c>
       <c r="AG154" t="n">
-        <v>2464</v>
+        <v>753</v>
       </c>
       <c r="AH154" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="AI154" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="AJ154" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="AK154" t="n">
-        <v>10</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="155">
@@ -19542,19 +19530,19 @@
         <v>1867</v>
       </c>
       <c r="AG155" t="n">
-        <v>2323</v>
+        <v>859</v>
       </c>
       <c r="AH155" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="AI155" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AJ155" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AK155" t="n">
-        <v>0</v>
+        <v>1732</v>
       </c>
     </row>
   </sheetData>
